--- a/src/data/current_data/bios_currentdata.xlsx
+++ b/src/data/current_data/bios_currentdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vanessachok/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riya/Desktop/dspuci-website-gatsby/dspuci-website-gatsby/src/data/current_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B776EB-7135-3E4B-931C-731C58477FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76C6E81-7CE6-9B47-81DB-55E7AED592FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2740" yWindow="2920" windowWidth="24480" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -555,15 +555,6 @@
     <t>Psychology</t>
   </si>
   <si>
-    <t>Project Management, Product Management</t>
-  </si>
-  <si>
-    <t>Specialty Masters Program Student Assistant @ Paul Merage School of Business</t>
-  </si>
-  <si>
-    <t>MAISS, Product Association</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/riya-kapadekar/</t>
   </si>
   <si>
@@ -1138,9 +1129,6 @@
     <t>Marketing, Finance</t>
   </si>
   <si>
-    <t>Lead Instructor @ Mathnasium</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/sanika-patwardhan/</t>
   </si>
   <si>
@@ -1655,6 +1643,18 @@
   </si>
   <si>
     <t>Moraga, CA</t>
+  </si>
+  <si>
+    <t>Marketing Intern @ HawkRobo right</t>
+  </si>
+  <si>
+    <t>Product Management, Project Management</t>
+  </si>
+  <si>
+    <t>Incoming Innotech Data, Experience &amp; Product Intern @ CVS Health</t>
+  </si>
+  <si>
+    <t>Product Association, Design @ UCI</t>
   </si>
 </sst>
 </file>
@@ -1825,7 +1825,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1888,19 +1888,8 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2308,32 +2297,32 @@
         <v>31</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>31</v>
@@ -2341,61 +2330,61 @@
       <c r="M4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="32" t="s">
-        <v>522</v>
-      </c>
-      <c r="O4" s="32" t="s">
-        <v>520</v>
+      <c r="N4" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="O4" s="28" t="s">
+        <v>516</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="32">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="30" t="s">
+      <c r="I5" s="10"/>
+      <c r="J5" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="30" t="s">
+      <c r="L5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="31" t="s">
+      <c r="M5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="O5" s="29" t="s">
+      <c r="O5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="P5" s="11" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2404,47 +2393,47 @@
         <v>31</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>83</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>75</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -2490,7 +2479,7 @@
         <v>62</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>27</v>
@@ -2846,22 +2835,22 @@
         <v>31</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>128</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>38</v>
@@ -2870,25 +2859,25 @@
         <v>95</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>31</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>123</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="O14" s="25" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -2896,49 +2885,49 @@
         <v>31</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="L15" s="26" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>123</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="P15" s="26" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -3144,25 +3133,25 @@
         <v>175</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>176</v>
+        <v>540</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>177</v>
+        <v>541</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>178</v>
+        <v>542</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>27</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="32">
@@ -3170,13 +3159,13 @@
         <v>31</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>130</v>
@@ -3185,34 +3174,34 @@
         <v>93</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I20" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="16">
@@ -3220,13 +3209,13 @@
         <v>31</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>35</v>
@@ -3235,32 +3224,32 @@
         <v>93</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>83</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="M21" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="N21" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="O21" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="P21" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
@@ -3278,13 +3267,13 @@
         <v>31</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>35</v>
@@ -3293,32 +3282,32 @@
         <v>36</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>112</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
@@ -3336,13 +3325,13 @@
         <v>31</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>35</v>
@@ -3358,7 +3347,7 @@
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>31</v>
@@ -3370,13 +3359,13 @@
         <v>123</v>
       </c>
       <c r="N23" s="19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="32">
@@ -3384,13 +3373,13 @@
         <v>31</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>49</v>
@@ -3399,32 +3388,32 @@
         <v>21</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="M24" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="N24" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="O24" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="M24" s="4" t="s">
+      <c r="P24" s="11" t="s">
         <v>230</v>
-      </c>
-      <c r="N24" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="O24" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="P24" s="11" t="s">
-        <v>233</v>
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
@@ -3442,47 +3431,47 @@
         <v>31</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="M25" s="10" t="s">
         <v>75</v>
       </c>
       <c r="N25" s="24" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="O25" s="24" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="32">
@@ -3490,13 +3479,13 @@
         <v>31</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>139</v>
@@ -3505,32 +3494,32 @@
         <v>93</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>83</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N26" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="O26" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="P26" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:26">
@@ -3538,47 +3527,47 @@
         <v>31</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>83</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M27" s="10" t="s">
         <v>123</v>
       </c>
       <c r="N27" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="O27" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="P27" s="10" t="s">
         <v>532</v>
-      </c>
-      <c r="O27" s="25" t="s">
-        <v>533</v>
-      </c>
-      <c r="P27" s="10" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
@@ -3586,13 +3575,13 @@
         <v>31</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>139</v>
@@ -3601,32 +3590,32 @@
         <v>93</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>27</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P28" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -3644,13 +3633,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>35</v>
@@ -3659,32 +3648,32 @@
         <v>93</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>123</v>
       </c>
       <c r="N29" s="19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P29" s="11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -3702,47 +3691,47 @@
         <v>31</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="F30" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>460</v>
-      </c>
       <c r="G30" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="10" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>112</v>
       </c>
       <c r="N30" s="24" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="O30" s="24" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
@@ -3750,13 +3739,13 @@
         <v>31</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>130</v>
@@ -3765,14 +3754,14 @@
         <v>93</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>85</v>
@@ -3784,13 +3773,13 @@
         <v>75</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
@@ -3798,13 +3787,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>20</v>
@@ -3820,25 +3809,25 @@
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="N32" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="O32" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="P32" s="11" t="s">
         <v>290</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="N32" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="O32" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="P32" s="11" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
@@ -3846,13 +3835,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>20</v>
@@ -3861,17 +3850,17 @@
         <v>21</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="L33" s="10" t="s">
         <v>31</v>
@@ -3880,13 +3869,13 @@
         <v>75</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
@@ -3904,13 +3893,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>20</v>
@@ -3919,32 +3908,32 @@
         <v>36</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N34" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="O34" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="P34" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="O34" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
@@ -3962,47 +3951,47 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="F35" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="G35" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="20" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M35" s="10" t="s">
         <v>123</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P35" s="20" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
@@ -4020,13 +4009,13 @@
         <v>31</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>20</v>
@@ -4035,32 +4024,32 @@
         <v>21</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>70</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N36" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="O36" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="L36" s="4" t="s">
+      <c r="P36" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="N36" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="O36" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="P36" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
@@ -4078,13 +4067,13 @@
         <v>31</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>35</v>
@@ -4093,34 +4082,34 @@
         <v>36</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="J37" s="9" t="s">
         <v>328</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>331</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>31</v>
       </c>
       <c r="L37" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="N37" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="M37" s="9" t="s">
+      <c r="P37" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="N37" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>336</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
@@ -4138,13 +4127,13 @@
         <v>31</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>130</v>
@@ -4153,32 +4142,32 @@
         <v>93</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>83</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>27</v>
       </c>
       <c r="N38" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -4196,13 +4185,13 @@
         <v>31</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>49</v>
@@ -4211,32 +4200,32 @@
         <v>36</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>60</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="13" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="M39" s="10" t="s">
         <v>27</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P39" s="13" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1">
@@ -4244,13 +4233,13 @@
         <v>31</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>20</v>
@@ -4259,7 +4248,7 @@
         <v>21</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>107</v>
@@ -4272,19 +4261,19 @@
         <v>31</v>
       </c>
       <c r="L40" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N40" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="O40" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="M40" s="4" t="s">
+      <c r="P40" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="N40" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="O40" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1">
@@ -4292,13 +4281,13 @@
         <v>31</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>20</v>
@@ -4310,31 +4299,31 @@
         <v>22</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>95</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>370</v>
+        <v>539</v>
       </c>
       <c r="L41" s="11" t="s">
         <v>74</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N41" s="22" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1">
@@ -4342,47 +4331,47 @@
         <v>31</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F42" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="10" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="K42" s="10" t="s">
         <v>31</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="M42" s="10" t="s">
         <v>112</v>
       </c>
       <c r="N42" s="24" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="O42" s="25" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="P42" s="10" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
@@ -4400,13 +4389,13 @@
         <v>31</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>35</v>
@@ -4415,32 +4404,32 @@
         <v>93</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>75</v>
       </c>
       <c r="N43" s="7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
@@ -4448,13 +4437,13 @@
         <v>31</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>130</v>
@@ -4466,29 +4455,29 @@
         <v>153</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="O44" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="K44" s="4" t="s">
+      <c r="P44" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="N44" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
@@ -4496,13 +4485,13 @@
         <v>31</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>139</v>
@@ -4511,7 +4500,7 @@
         <v>93</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>83</v>
@@ -4520,25 +4509,25 @@
         <v>95</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>75</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1">
@@ -4546,13 +4535,13 @@
         <v>31</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>35</v>
@@ -4561,32 +4550,32 @@
         <v>36</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>83</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="M46" s="4" t="s">
         <v>112</v>
       </c>
       <c r="N46" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
@@ -4594,47 +4583,47 @@
         <v>31</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="M47" s="10" t="s">
         <v>112</v>
       </c>
       <c r="N47" s="24" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="O47" s="25" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1">
@@ -4642,13 +4631,13 @@
         <v>31</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>49</v>
@@ -4657,34 +4646,34 @@
         <v>36</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="J48" s="13" t="s">
         <v>144</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M48" s="10" t="s">
         <v>123</v>
       </c>
       <c r="N48" s="12" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="O48" s="10" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="P48" s="13" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="15.75" customHeight="1">
@@ -4692,13 +4681,13 @@
         <v>31</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>35</v>
@@ -4714,25 +4703,25 @@
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>135</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="N49" s="19" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="15.75" customHeight="1">
@@ -4740,13 +4729,13 @@
         <v>31</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>49</v>
@@ -4755,32 +4744,32 @@
         <v>21</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>83</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="11" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>27</v>
       </c>
       <c r="N50" s="12" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="O50" s="10" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="P50" s="11" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="15.75" customHeight="1">
@@ -4788,13 +4777,13 @@
         <v>31</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>139</v>
@@ -4803,34 +4792,34 @@
         <v>93</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>84</v>
       </c>
       <c r="K51" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N51" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="P51" s="11" t="s">
         <v>443</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>444</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="N51" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="O51" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="P51" s="11" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="15.75" customHeight="1">
@@ -4838,13 +4827,13 @@
         <v>31</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>49</v>
@@ -4853,32 +4842,32 @@
         <v>21</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="M52" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="O52" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="P52" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="L52" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="M52" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="N52" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>454</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="15.75" customHeight="1">

--- a/src/data/current_data/bios_currentdata.xlsx
+++ b/src/data/current_data/bios_currentdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riya/Desktop/dspuci-website-gatsby/dspuci-website-gatsby/src/data/current_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76C6E81-7CE6-9B47-81DB-55E7AED592FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5A860B-325D-7649-9734-770A9037B199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2740" yWindow="2920" windowWidth="24480" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1645,9 +1645,6 @@
     <t>Moraga, CA</t>
   </si>
   <si>
-    <t>Marketing Intern @ HawkRobo right</t>
-  </si>
-  <si>
     <t>Product Management, Project Management</t>
   </si>
   <si>
@@ -1655,6 +1652,9 @@
   </si>
   <si>
     <t>Product Association, Design @ UCI</t>
+  </si>
+  <si>
+    <t>Marketing Intern @ HawkRobo</t>
   </si>
 </sst>
 </file>
@@ -3133,13 +3133,13 @@
         <v>175</v>
       </c>
       <c r="J19" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="K19" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="L19" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>542</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>27</v>
@@ -4308,7 +4308,7 @@
         <v>366</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L41" s="11" t="s">
         <v>74</v>

--- a/src/data/current_data/bios_currentdata.xlsx
+++ b/src/data/current_data/bios_currentdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riya/Desktop/dspuci-website-gatsby/dspuci-website-gatsby/src/data/current_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vanessachok/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5A860B-325D-7649-9734-770A9037B199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD156B02-DC42-7D44-93A4-70419BC47FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2740" yWindow="2920" windowWidth="24480" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="546">
   <si>
     <t>Timestamp</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Quant, Asset Management</t>
   </si>
   <si>
-    <t>Equity Research Intern @ Strategic Global Advisors</t>
-  </si>
-  <si>
     <t>180 Degrees Consulting</t>
   </si>
   <si>
@@ -147,9 +144,6 @@
     <t>Investment Banking, Private Equity, Entrepreneurship</t>
   </si>
   <si>
-    <t>Financial Analyst @ Firmly</t>
-  </si>
-  <si>
     <t>Kappa Sigma Fraternity</t>
   </si>
   <si>
@@ -213,9 +207,6 @@
     <t>Product Marketing, Strategy and Analytics, UI/UX Design</t>
   </si>
   <si>
-    <t>Intern @ Torrance Currency Exchange</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/vanessa-chok/</t>
   </si>
   <si>
@@ -246,9 +237,6 @@
     <t xml:space="preserve">Product Management, Data Science </t>
   </si>
   <si>
-    <t>Brand Ambassador @ Princess Polly</t>
-  </si>
-  <si>
     <t>MAISS</t>
   </si>
   <si>
@@ -282,9 +270,6 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>Audit Intern @ KPMG</t>
-  </si>
-  <si>
     <t>SMIF, ITG, UBA, KCM</t>
   </si>
   <si>
@@ -318,9 +303,6 @@
     <t>Consulting, Finance</t>
   </si>
   <si>
-    <t>Business Analyst Intern @ FTI Delta</t>
-  </si>
-  <si>
     <t>180 Degrees Consulting, Irvine Investment &amp; Trading Group, Scholars of Finance, Kababayan</t>
   </si>
   <si>
@@ -390,9 +372,6 @@
     <t>Consulting</t>
   </si>
   <si>
-    <t>Strategy Intern @ Breez Events and Consulting</t>
-  </si>
-  <si>
     <t>MAISS, Tennis Club</t>
   </si>
   <si>
@@ -429,9 +408,6 @@
     <t>Finance, Product Management, Data</t>
   </si>
   <si>
-    <t>Finance Intern @ Raytheon Technologies</t>
-  </si>
-  <si>
     <t>UBA</t>
   </si>
   <si>
@@ -462,9 +438,6 @@
     <t>Marketing, Product Management</t>
   </si>
   <si>
-    <t>Incoming Product Management Intern @ Mastercard</t>
-  </si>
-  <si>
     <t>Indian Subcontinental Club</t>
   </si>
   <si>
@@ -495,9 +468,6 @@
     <t>Law, Entrepreneurship, Finance</t>
   </si>
   <si>
-    <t>External Relations Assistant @ UCI Libraries</t>
-  </si>
-  <si>
     <t>ASUCI</t>
   </si>
   <si>
@@ -525,9 +495,6 @@
     <t>Product Management</t>
   </si>
   <si>
-    <t>Product Management Intern @ Stride</t>
-  </si>
-  <si>
     <t>180 Degrees Consulting, Product Association, MAISS</t>
   </si>
   <si>
@@ -582,9 +549,6 @@
     <t>Asset &amp; Wealth Management</t>
   </si>
   <si>
-    <t>Audit Intern @ EY</t>
-  </si>
-  <si>
     <t>SMIF, ITG, UBA</t>
   </si>
   <si>
@@ -648,9 +612,6 @@
     <t>Marketing</t>
   </si>
   <si>
-    <t>Red Bull Student Marketeer, Doordash Campus Launcher</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tri Delta </t>
   </si>
   <si>
@@ -735,9 +696,6 @@
     <t>Consulting, Finance, Wealth Management</t>
   </si>
   <si>
-    <t>Middle Market Business Specialized Industry Summer Analyst @ J.P. Morgan</t>
-  </si>
-  <si>
     <t>ASUCI, KCM</t>
   </si>
   <si>
@@ -765,9 +723,6 @@
     <t xml:space="preserve">Software Engineering </t>
   </si>
   <si>
-    <t>Supply Chain Technology Consulting Intern @ EY</t>
-  </si>
-  <si>
     <t>ITG, UBA</t>
   </si>
   <si>
@@ -798,9 +753,6 @@
     <t xml:space="preserve">Software Engineering, Product Management, Entrepreneurship </t>
   </si>
   <si>
-    <t>Technical Program Manager Intern @ PlayStation</t>
-  </si>
-  <si>
     <t>MAISS, Data@UCI, Google Student Developer Club</t>
   </si>
   <si>
@@ -858,9 +810,6 @@
     <t>Project Management, Product Marketing Management</t>
   </si>
   <si>
-    <t>Strategy &amp; Operations Analyst @ DoorDash | Graduate Brand Strategist @ SoFi</t>
-  </si>
-  <si>
     <t>Sports Business Association, Management Information Student Society, FBLA, Pakistani Student Association, Club Cricket</t>
   </si>
   <si>
@@ -885,9 +834,6 @@
     <t>Marketing, Entrepreneurship</t>
   </si>
   <si>
-    <t>Marketing Intern @ LensGen</t>
-  </si>
-  <si>
     <t xml:space="preserve">MAISS, Product Association, Dance Club </t>
   </si>
   <si>
@@ -915,9 +861,6 @@
     <t>Aerospace Engineering, Bullion, Forex</t>
   </si>
   <si>
-    <t>Student Researcher @ MIT</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/vansh-mehta-053655360/</t>
   </si>
   <si>
@@ -976,9 +919,6 @@
   </si>
   <si>
     <t>Software Engineering, Real Estate, Bullion</t>
-  </si>
-  <si>
-    <t>Co-Founder at Vior Sports [Nvidia]</t>
   </si>
   <si>
     <t>LBSA, AI @ UCI</t>
@@ -1045,9 +985,6 @@
     <t>Consulting, Accounting</t>
   </si>
   <si>
-    <t>Technology Risk Assurance Intern @ EY</t>
-  </si>
-  <si>
     <t>MBA Programs Student Assistant, Accounting Association</t>
   </si>
   <si>
@@ -1156,9 +1093,6 @@
     <t>Software Engineering, Product Management, Entrepreneurship</t>
   </si>
   <si>
-    <t>Product Management Intern @ Capital One</t>
-  </si>
-  <si>
     <t>UBA, Product Association</t>
   </si>
   <si>
@@ -1186,9 +1120,6 @@
     <t>Finance, Software Engineering, PM</t>
   </si>
   <si>
-    <t>AI Engineering Intern @ firmly</t>
-  </si>
-  <si>
     <t>Manifest, ITG, AI Club</t>
   </si>
   <si>
@@ -1213,9 +1144,6 @@
     <t>Cerritos, CA</t>
   </si>
   <si>
-    <t>Marketing Intern @ L'Oréal</t>
-  </si>
-  <si>
     <t>UBA, Product Association, Kababayan</t>
   </si>
   <si>
@@ -1240,9 +1168,6 @@
     <t>Operations, Project Management</t>
   </si>
   <si>
-    <t>Operations Intern @ Schneider National</t>
-  </si>
-  <si>
     <t>MUSA, Magic @ UCI</t>
   </si>
   <si>
@@ -1273,9 +1198,6 @@
     <t>Digital Arts, Spanish</t>
   </si>
   <si>
-    <t>Marketing Intern @ United Nations OC</t>
-  </si>
-  <si>
     <t>MAISS, GBB, SJP</t>
   </si>
   <si>
@@ -1297,9 +1219,6 @@
     <t>jadon_song</t>
   </si>
   <si>
-    <t>Growth Marketing Intern @ FOX Tech</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/jadon-song/</t>
   </si>
   <si>
@@ -1321,9 +1240,6 @@
     <t>Finance, Accounting, Computer Science</t>
   </si>
   <si>
-    <t>Fixed Income Sales and Trading Intern @ Great Pacific Securities</t>
-  </si>
-  <si>
     <t>UCI Men’s Club Rowing, UBA, MUSA</t>
   </si>
   <si>
@@ -1345,9 +1261,6 @@
     <t>tommy_wunsch</t>
   </si>
   <si>
-    <t xml:space="preserve">Incoming Analyst @ J.P. Morgan. </t>
-  </si>
-  <si>
     <t xml:space="preserve">SMIF, 180 Degrees Consulting, UBA, Merage MBA Program Services Office </t>
   </si>
   <si>
@@ -1372,9 +1285,6 @@
     <t>Software Engineering, Product Management</t>
   </si>
   <si>
-    <t>Software Engineering Intern @ Gatekeeper Systems</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/tiffzhny/</t>
   </si>
   <si>
@@ -1402,9 +1312,6 @@
     <t xml:space="preserve">Marketing, UI/UX Design, Product Management </t>
   </si>
   <si>
-    <t>Bubble Campus Ambassador</t>
-  </si>
-  <si>
     <t>Design @ UCI, MAISS</t>
   </si>
   <si>
@@ -1501,9 +1408,6 @@
     <t>gavin_han</t>
   </si>
   <si>
-    <t>Model @ Nomad Management</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/hhan81/</t>
   </si>
   <si>
@@ -1516,9 +1420,6 @@
     <t>Product Marketing, Corporate Fashion, UI/UX</t>
   </si>
   <si>
-    <t>Design @ UCI, UBA, MAISS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hi! I'm Daisy and I initiated with the Alpha Upsilon's! In my free time I love running and hiking in nature, reading, going to the beach, and finding new matcha places to try:) Ask me about my go-to coffee recipe or good running trails in Irvine at recruitment. </t>
   </si>
   <si>
@@ -1543,9 +1444,6 @@
     <t>Finance, Consulting</t>
   </si>
   <si>
-    <t>Sales Representative @ Vector Marketing</t>
-  </si>
-  <si>
     <t>ITG</t>
   </si>
   <si>
@@ -1573,9 +1471,6 @@
     <t>AI, Finance</t>
   </si>
   <si>
-    <t>Quant Research @ IVC</t>
-  </si>
-  <si>
     <t>atharvattri@ucidsp.com</t>
   </si>
   <si>
@@ -1591,9 +1486,6 @@
     <t>Quantitative Economics</t>
   </si>
   <si>
-    <t>Hi my name is Atharv and I initiated in the fall of my third year with the Alpha Upsilons. Ask me anything at recruitment!</t>
-  </si>
-  <si>
     <t>Thea</t>
   </si>
   <si>
@@ -1609,9 +1501,6 @@
     <t>San Francisco, CA</t>
   </si>
   <si>
-    <t>Marketing Intern @ RMW Architecture &amp; Interiors</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/laurenwlew/</t>
   </si>
   <si>
@@ -1636,9 +1525,6 @@
     <t>Investment Banking, Finance</t>
   </si>
   <si>
-    <t>Investment Analyst Intern @ SGI Capital</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hi, my name is Thea. I initiated in the fall quarter of my first year with the Alpha Upsilon class. In my free time, I enjoy playing pickleball, going to the beach, and shopping. Ask me about the show Friends and my love for dad jokes at recruitment! </t>
   </si>
   <si>
@@ -1655,6 +1541,129 @@
   </si>
   <si>
     <t>Marketing Intern @ HawkRobo</t>
+  </si>
+  <si>
+    <t>Design @ UCI, UBA, MAISS, Fits</t>
+  </si>
+  <si>
+    <t>Incoming Strategy Intern @ Experian</t>
+  </si>
+  <si>
+    <t>Private Equity Spring Analyst @ KPMG</t>
+  </si>
+  <si>
+    <t>Product Management Intern @ Tallo, Incoming Product Management Intern @ Capital One</t>
+  </si>
+  <si>
+    <t>Incoming Product Management Intern @ Mastercard, Incoming Global Private Banking Analyst @ JPMorgan Chase &amp; Co.</t>
+  </si>
+  <si>
+    <t>Brand Ambassador @ Princess Polly, Software Engineering Intern @ Community Innovations Foundation</t>
+  </si>
+  <si>
+    <t>Undergraduate Researcher @ UC Irvine</t>
+  </si>
+  <si>
+    <t>Strategy Intern @ Middlebury Education</t>
+  </si>
+  <si>
+    <t>Campus Growth Intern @ Ditto</t>
+  </si>
+  <si>
+    <t>Model @ Nomad Management, Campus Growth Intern @ Ditto</t>
+  </si>
+  <si>
+    <t>Growth Marketing/CRM Intern @ FOX</t>
+  </si>
+  <si>
+    <t>Financial Analyst Intern @ Rostrum Grand Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incoming Commerical Banking Intern @ Wells Fargo, Intern @ Concordia Capital </t>
+  </si>
+  <si>
+    <t>Incoming Private Equity Analyst Intern @ Tigbourne Capital Ltd</t>
+  </si>
+  <si>
+    <t>Marketing Intern @ Depop</t>
+  </si>
+  <si>
+    <t>Product Ambassador @ Ditto</t>
+  </si>
+  <si>
+    <t>Software Engineering Intern @ FOX</t>
+  </si>
+  <si>
+    <t>AI Engineering Intern @ Firmly, Incoming Forward Deployed AI Engineer @ BCG X</t>
+  </si>
+  <si>
+    <t>Incoming Marketing Intern @ Crusoe AI</t>
+  </si>
+  <si>
+    <t>Audit Intern @ KPMG, Incoming Credit Analyst Intern @ BMO</t>
+  </si>
+  <si>
+    <t>Supply Chain Intern @ Southern California Edison</t>
+  </si>
+  <si>
+    <t>Incoming Financial Analyst Intern @ Expedia Group</t>
+  </si>
+  <si>
+    <t>Investment Banking Summer Analyst @ CB Capital Partners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incoming Risk and Financial Advisory Intern @ Deloitte </t>
+  </si>
+  <si>
+    <t>Software Engineering Intern @ BMW, Incoming Software Engineering Intern @ Google</t>
+  </si>
+  <si>
+    <t>Red Bull Student Marketeer, Creator Partnerships Intern @ Wasserman</t>
+  </si>
+  <si>
+    <t>Single Wing Team Lead @ FWMAV UCI</t>
+  </si>
+  <si>
+    <t>Incoming Technical Program Manager @ Applied Materials</t>
+  </si>
+  <si>
+    <t>Incoming Business Associate @ VISA</t>
+  </si>
+  <si>
+    <t>Incoming Technology Risk Assurance @ EY</t>
+  </si>
+  <si>
+    <t>Incoming Audit Associate @ KPMG</t>
+  </si>
+  <si>
+    <t>Incoming Analyst @ JPMorgan Chase &amp; Co.</t>
+  </si>
+  <si>
+    <t>Incoming Audit Associate @ EY</t>
+  </si>
+  <si>
+    <t>Incoming Technology Consultant @ EY</t>
+  </si>
+  <si>
+    <t>Incoming Associate Product Manager @ Capital One</t>
+  </si>
+  <si>
+    <t>Incoming Marketing Management Trainee @ L'Oreal</t>
+  </si>
+  <si>
+    <t>Strategy and Operations Analyst @ DoorDash</t>
+  </si>
+  <si>
+    <t>Incoming Consultant @ FTI Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incoming Analyst @ JPMorgan Chase &amp; Co. </t>
+  </si>
+  <si>
+    <t>Math Finance Club, ISC</t>
+  </si>
+  <si>
+    <t>Hello! My name is Atharv and I initiated the fall quarter of my third year with the Alpha Upsilons! I love listening to muisc, driving, planes, and going to the beach! Talk to me about anything at recruitment and tell me your favorite song!</t>
   </si>
 </sst>
 </file>
@@ -2206,22 +2215,22 @@
         <v>24</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
@@ -2236,50 +2245,50 @@
     </row>
     <row r="3" spans="1:26" ht="18.75" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="N3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="P3" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
@@ -2294,67 +2303,67 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>510</v>
+        <v>476</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>512</v>
+        <v>478</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8" t="s">
-        <v>514</v>
+        <v>480</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>31</v>
+        <v>544</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N4" s="28" t="s">
-        <v>518</v>
+        <v>483</v>
       </c>
       <c r="O4" s="28" t="s">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>521</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="32">
       <c r="A5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>21</v>
@@ -2363,77 +2372,77 @@
         <v>22</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="M5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="O5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="29" t="s">
+      <c r="P5" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>506</v>
+        <v>472</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>509</v>
+        <v>475</v>
       </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -2448,64 +2457,64 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="E7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>60</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="P7" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="P7" s="11" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="32">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>20</v>
@@ -2514,34 +2523,34 @@
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="K8" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="L8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="M8" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="N8" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="O8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="P8" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -2554,52 +2563,52 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="16">
+    <row r="9" spans="1:26" ht="32">
       <c r="A9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="13" t="s">
         <v>79</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>83</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="P9" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -2614,52 +2623,52 @@
     </row>
     <row r="10" spans="1:26" ht="32">
       <c r="A10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="K10" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="M10" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="N10" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="O10" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="P10" s="15" t="s">
         <v>96</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="P10" s="15" t="s">
-        <v>102</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -2674,16 +2683,16 @@
     </row>
     <row r="11" spans="1:26" ht="16">
       <c r="A11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>20</v>
@@ -2692,34 +2701,34 @@
         <v>21</v>
       </c>
       <c r="G11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="N11" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="O11" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="P11" s="9" t="s">
         <v>109</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -2734,16 +2743,16 @@
     </row>
     <row r="12" spans="1:26" ht="16">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>20</v>
@@ -2752,230 +2761,230 @@
         <v>21</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>121</v>
+        <v>512</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="16">
       <c r="A13" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="M13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="O13" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="P13" s="9" t="s">
         <v>130</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>466</v>
+        <v>435</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>31</v>
+        <v>516</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="O14" s="25" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>471</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="L15" s="26" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="P15" s="26" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="10" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>145</v>
+        <v>509</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -2988,52 +2997,52 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="16">
+    <row r="17" spans="1:26" ht="32">
       <c r="A17" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>156</v>
+        <v>526</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -3048,50 +3057,50 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>166</v>
+        <v>508</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="P18" s="11" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -3106,150 +3115,150 @@
     </row>
     <row r="19" spans="1:26" ht="16">
       <c r="A19" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>539</v>
+        <v>501</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>540</v>
+        <v>502</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>541</v>
+        <v>503</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="32">
       <c r="A20" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>185</v>
+        <v>537</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="16">
       <c r="A21" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
@@ -3264,50 +3273,50 @@
     </row>
     <row r="22" spans="1:26" ht="16">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="G22" s="4" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>207</v>
+        <v>530</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
@@ -3322,98 +3331,98 @@
     </row>
     <row r="23" spans="1:26" ht="16">
       <c r="A23" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="9" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N23" s="19" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="32">
       <c r="A24" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="13" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="O24" s="10" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="P24" s="11" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
@@ -3428,194 +3437,194 @@
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>522</v>
+        <v>486</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>533</v>
+        <v>496</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>523</v>
+        <v>487</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10" t="s">
-        <v>535</v>
+        <v>498</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N25" s="24" t="s">
-        <v>519</v>
+        <v>484</v>
       </c>
       <c r="O25" s="24" t="s">
-        <v>517</v>
+        <v>482</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" ht="32">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" ht="16">
       <c r="A26" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>236</v>
+        <v>536</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="P26" s="9" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>524</v>
+        <v>488</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>525</v>
+        <v>489</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>526</v>
+        <v>490</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10" t="s">
-        <v>531</v>
+        <v>494</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N27" s="24" t="s">
-        <v>528</v>
+        <v>491</v>
       </c>
       <c r="O27" s="25" t="s">
-        <v>529</v>
+        <v>492</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>532</v>
+        <v>495</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>246</v>
+        <v>538</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="P28" s="9" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -3630,50 +3639,50 @@
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="9" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>257</v>
+        <v>532</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N29" s="19" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="P29" s="11" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -3688,112 +3697,112 @@
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>452</v>
+        <v>422</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>453</v>
+        <v>423</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>454</v>
+        <v>424</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="10" t="s">
-        <v>457</v>
+        <v>427</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N30" s="24" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="O30" s="24" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>20</v>
@@ -3805,43 +3814,43 @@
         <v>22</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="11" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>286</v>
+        <v>523</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="O32" s="10" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="P32" s="11" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>20</v>
@@ -3850,32 +3859,32 @@
         <v>21</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="10" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>296</v>
+        <v>531</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
@@ -3890,50 +3899,50 @@
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="11" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
@@ -3948,50 +3957,50 @@
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="20" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>277</v>
+        <v>541</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="P35" s="20" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
@@ -4006,16 +4015,16 @@
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>20</v>
@@ -4024,32 +4033,32 @@
         <v>21</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>317</v>
+        <v>521</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
@@ -4064,52 +4073,52 @@
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1">
       <c r="A37" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="E37" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="G37" s="9" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="N37" s="19" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
@@ -4124,50 +4133,50 @@
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="9" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>339</v>
+        <v>534</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N38" s="7" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -4182,64 +4191,64 @@
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1">
       <c r="A39" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="13" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="P39" s="13" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>20</v>
@@ -4248,46 +4257,46 @@
         <v>21</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>31</v>
+        <v>507</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="N40" s="22" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>20</v>
@@ -4299,79 +4308,79 @@
         <v>22</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>542</v>
+        <v>504</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N41" s="22" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1">
       <c r="A42" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>482</v>
+        <v>451</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F42" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>538</v>
+        <v>500</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="10" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N42" s="24" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="O42" s="25" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="P42" s="10" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
@@ -4386,488 +4395,488 @@
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>376</v>
+        <v>539</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N43" s="7" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>386</v>
+        <v>522</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>395</v>
+        <v>540</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1">
       <c r="A46" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="E46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="G46" s="4" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>404</v>
+        <v>525</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N46" s="7" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
       <c r="A47" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>472</v>
+        <v>441</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N47" s="24" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="O47" s="25" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>415</v>
+        <v>523</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N48" s="12" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="O48" s="10" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="P48" s="13" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="15.75" customHeight="1">
       <c r="A49" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>423</v>
+        <v>515</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="N49" s="19" t="s">
-        <v>424</v>
+        <v>397</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>425</v>
+        <v>398</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="15.75" customHeight="1">
       <c r="A50" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>427</v>
+        <v>400</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>428</v>
+        <v>401</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="11" t="s">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>431</v>
+        <v>517</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N50" s="12" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="O50" s="10" t="s">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="P50" s="11" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="15.75" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>439</v>
+        <v>543</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N51" s="7" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="P51" s="11" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="15.75" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="10" t="s">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="N52" s="12" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="O52" s="10" t="s">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>451</v>
+        <v>421</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="15.75" customHeight="1">

--- a/src/data/current_data/bios_currentdata.xlsx
+++ b/src/data/current_data/bios_currentdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vanessachok/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD156B02-DC42-7D44-93A4-70419BC47FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D5F8D3-7273-D946-A267-04E03FBDE17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4854,7 +4854,7 @@
         <v>325</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>353</v>
+        <v>444</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="10" t="s">
